--- a/tool/kintone-aggregator/master/地域共催.xlsx
+++ b/tool/kintone-aggregator/master/地域共催.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\businessImprovement\tool\提出確認\master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6784F7FE-5513-43CB-8068-40D14645E660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3B2F0E-4319-4165-8E78-CE2AE49AC65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="585">
   <si>
     <t>氏名</t>
     <rPh sb="0" eb="2">
@@ -89,38 +89,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>アルゴリズム入門</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>データベース技術入門</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>Web技術入門</t>
-  </si>
-  <si>
-    <t>Javaプログラミング基礎</t>
-  </si>
-  <si>
-    <t>Javaプログラミング応用</t>
-    <rPh sb="11" eb="13">
-      <t>オウヨウ</t>
-    </rPh>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>サービスデザイン</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>開発プロセス</t>
-  </si>
-  <si>
-    <t>テクニカル総合演習</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>Grp61-2026001</t>
   </si>
   <si>
@@ -1847,14 +1815,6 @@
   </si>
   <si>
     <t>社会を支えるITサービス</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>基本スキル or ビジネス基礎</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>企業活動入門</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1865,7 +1825,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2033,12 +1993,6 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2501,7 +2455,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -2909,16 +2863,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="E2" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -2930,16 +2884,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="E3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -2951,16 +2905,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -2972,16 +2926,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="E5" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -2993,16 +2947,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E6" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -3014,16 +2968,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E7" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -3035,16 +2989,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E8" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -3056,16 +3010,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E9" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -3077,16 +3031,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E10" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -3098,16 +3052,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E11" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -3119,16 +3073,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -3140,16 +3094,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E13" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -3161,16 +3115,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E14" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -3182,16 +3136,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="E15" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -3203,16 +3157,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="E16" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -3224,16 +3178,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="E17" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -3245,16 +3199,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E18" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
@@ -3266,16 +3220,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E19" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
@@ -3287,16 +3241,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E20" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -3308,16 +3262,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E21" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -3329,16 +3283,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E22" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -3350,16 +3304,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="E23" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -3371,16 +3325,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E24" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -3392,16 +3346,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E25" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -3413,16 +3367,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E26" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -3434,16 +3388,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E27" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -3455,16 +3409,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E28" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -3476,16 +3430,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="E29" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -3497,16 +3451,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E30" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -3518,16 +3472,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="E31" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -3539,16 +3493,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="E32" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
@@ -3560,16 +3514,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="E33" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -3581,16 +3535,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E34" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
@@ -3602,16 +3556,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="E35" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
@@ -3623,16 +3577,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="E36" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
@@ -3644,16 +3598,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E37" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
@@ -3665,16 +3619,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="E38" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
@@ -3686,16 +3640,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D39" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E39" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
@@ -3707,16 +3661,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="E40" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
@@ -3728,16 +3682,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="E41" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
@@ -3749,16 +3703,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E42" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
@@ -3770,16 +3724,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="E43" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
@@ -3791,16 +3745,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D44" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="E44" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
@@ -3812,16 +3766,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E45" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -3833,16 +3787,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D46" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E46" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
@@ -3854,16 +3808,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D47" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="E47" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -3875,16 +3829,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D48" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="E48" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -3896,16 +3850,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D49" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="E49" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -3917,16 +3871,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D50" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="E50" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -3938,16 +3892,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D51" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E51" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
@@ -3959,16 +3913,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C52" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D52" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E52" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -3980,16 +3934,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C53" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D53" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E53" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -4001,16 +3955,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>291</v>
+      </c>
+      <c r="C54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54" t="s">
+        <v>356</v>
+      </c>
+      <c r="E54" t="s">
         <v>299</v>
-      </c>
-      <c r="C54" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" t="s">
-        <v>364</v>
-      </c>
-      <c r="E54" t="s">
-        <v>307</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -4022,16 +3976,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>291</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" t="s">
+        <v>357</v>
+      </c>
+      <c r="E55" t="s">
         <v>299</v>
-      </c>
-      <c r="C55" t="s">
-        <v>70</v>
-      </c>
-      <c r="D55" t="s">
-        <v>365</v>
-      </c>
-      <c r="E55" t="s">
-        <v>307</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
@@ -4043,16 +3997,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>291</v>
+      </c>
+      <c r="C56" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" t="s">
+        <v>358</v>
+      </c>
+      <c r="E56" t="s">
         <v>299</v>
-      </c>
-      <c r="C56" t="s">
-        <v>71</v>
-      </c>
-      <c r="D56" t="s">
-        <v>366</v>
-      </c>
-      <c r="E56" t="s">
-        <v>307</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
@@ -4064,16 +4018,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>291</v>
+      </c>
+      <c r="C57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" t="s">
+        <v>359</v>
+      </c>
+      <c r="E57" t="s">
         <v>299</v>
-      </c>
-      <c r="C57" t="s">
-        <v>72</v>
-      </c>
-      <c r="D57" t="s">
-        <v>367</v>
-      </c>
-      <c r="E57" t="s">
-        <v>307</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
@@ -4085,16 +4039,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>291</v>
+      </c>
+      <c r="C58" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" t="s">
+        <v>360</v>
+      </c>
+      <c r="E58" t="s">
         <v>299</v>
-      </c>
-      <c r="C58" t="s">
-        <v>73</v>
-      </c>
-      <c r="D58" t="s">
-        <v>368</v>
-      </c>
-      <c r="E58" t="s">
-        <v>307</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
@@ -4106,16 +4060,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>291</v>
+      </c>
+      <c r="C59" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" t="s">
+        <v>361</v>
+      </c>
+      <c r="E59" t="s">
         <v>299</v>
-      </c>
-      <c r="C59" t="s">
-        <v>74</v>
-      </c>
-      <c r="D59" t="s">
-        <v>369</v>
-      </c>
-      <c r="E59" t="s">
-        <v>307</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
@@ -4127,16 +4081,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C60" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D60" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E60" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
@@ -4148,16 +4102,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D61" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E61" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
@@ -4169,16 +4123,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C62" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D62" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E62" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
@@ -4190,16 +4144,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>291</v>
+      </c>
+      <c r="C63" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" t="s">
+        <v>365</v>
+      </c>
+      <c r="E63" t="s">
         <v>299</v>
-      </c>
-      <c r="C63" t="s">
-        <v>78</v>
-      </c>
-      <c r="D63" t="s">
-        <v>373</v>
-      </c>
-      <c r="E63" t="s">
-        <v>307</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
@@ -4211,16 +4165,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D64" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E64" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
@@ -4232,16 +4186,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>291</v>
+      </c>
+      <c r="C65" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" t="s">
+        <v>367</v>
+      </c>
+      <c r="E65" t="s">
         <v>299</v>
-      </c>
-      <c r="C65" t="s">
-        <v>80</v>
-      </c>
-      <c r="D65" t="s">
-        <v>375</v>
-      </c>
-      <c r="E65" t="s">
-        <v>307</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
@@ -4253,16 +4207,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>291</v>
+      </c>
+      <c r="C66" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" t="s">
+        <v>368</v>
+      </c>
+      <c r="E66" t="s">
         <v>299</v>
-      </c>
-      <c r="C66" t="s">
-        <v>81</v>
-      </c>
-      <c r="D66" t="s">
-        <v>376</v>
-      </c>
-      <c r="E66" t="s">
-        <v>307</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
@@ -4274,16 +4228,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>291</v>
+      </c>
+      <c r="C67" t="s">
+        <v>74</v>
+      </c>
+      <c r="D67" t="s">
+        <v>369</v>
+      </c>
+      <c r="E67" t="s">
         <v>299</v>
-      </c>
-      <c r="C67" t="s">
-        <v>82</v>
-      </c>
-      <c r="D67" t="s">
-        <v>377</v>
-      </c>
-      <c r="E67" t="s">
-        <v>307</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
@@ -4295,16 +4249,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>291</v>
+      </c>
+      <c r="C68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" t="s">
+        <v>370</v>
+      </c>
+      <c r="E68" t="s">
         <v>299</v>
-      </c>
-      <c r="C68" t="s">
-        <v>83</v>
-      </c>
-      <c r="D68" t="s">
-        <v>378</v>
-      </c>
-      <c r="E68" t="s">
-        <v>307</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
@@ -4316,16 +4270,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D69" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E69" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
@@ -4337,16 +4291,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C70" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D70" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="E70" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
@@ -4358,16 +4312,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C71" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="E71" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F71" t="b">
         <v>0</v>
@@ -4379,16 +4333,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C72" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D72" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="E72" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
@@ -4400,16 +4354,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>292</v>
+      </c>
+      <c r="C73" t="s">
+        <v>80</v>
+      </c>
+      <c r="D73" t="s">
+        <v>375</v>
+      </c>
+      <c r="E73" t="s">
         <v>300</v>
-      </c>
-      <c r="C73" t="s">
-        <v>88</v>
-      </c>
-      <c r="D73" t="s">
-        <v>383</v>
-      </c>
-      <c r="E73" t="s">
-        <v>308</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
@@ -4421,16 +4375,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>292</v>
+      </c>
+      <c r="C74" t="s">
+        <v>81</v>
+      </c>
+      <c r="D74" t="s">
+        <v>376</v>
+      </c>
+      <c r="E74" t="s">
         <v>300</v>
-      </c>
-      <c r="C74" t="s">
-        <v>89</v>
-      </c>
-      <c r="D74" t="s">
-        <v>384</v>
-      </c>
-      <c r="E74" t="s">
-        <v>308</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
@@ -4442,16 +4396,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C75" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D75" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="E75" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F75" t="b">
         <v>0</v>
@@ -4463,16 +4417,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C76" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D76" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="E76" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F76" t="b">
         <v>0</v>
@@ -4484,16 +4438,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C77" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D77" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="E77" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F77" t="b">
         <v>0</v>
@@ -4505,16 +4459,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>292</v>
+      </c>
+      <c r="C78" t="s">
+        <v>85</v>
+      </c>
+      <c r="D78" t="s">
+        <v>380</v>
+      </c>
+      <c r="E78" t="s">
         <v>300</v>
-      </c>
-      <c r="C78" t="s">
-        <v>93</v>
-      </c>
-      <c r="D78" t="s">
-        <v>388</v>
-      </c>
-      <c r="E78" t="s">
-        <v>308</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
@@ -4526,16 +4480,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>292</v>
+      </c>
+      <c r="C79" t="s">
+        <v>86</v>
+      </c>
+      <c r="D79" t="s">
+        <v>381</v>
+      </c>
+      <c r="E79" t="s">
         <v>300</v>
-      </c>
-      <c r="C79" t="s">
-        <v>94</v>
-      </c>
-      <c r="D79" t="s">
-        <v>389</v>
-      </c>
-      <c r="E79" t="s">
-        <v>308</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
@@ -4547,16 +4501,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>292</v>
+      </c>
+      <c r="C80" t="s">
+        <v>87</v>
+      </c>
+      <c r="D80" t="s">
+        <v>382</v>
+      </c>
+      <c r="E80" t="s">
         <v>300</v>
-      </c>
-      <c r="C80" t="s">
-        <v>95</v>
-      </c>
-      <c r="D80" t="s">
-        <v>390</v>
-      </c>
-      <c r="E80" t="s">
-        <v>308</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
@@ -4568,16 +4522,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D81" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="E81" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -4589,16 +4543,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D82" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E82" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -4610,16 +4564,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>292</v>
+      </c>
+      <c r="C83" t="s">
+        <v>90</v>
+      </c>
+      <c r="D83" t="s">
+        <v>385</v>
+      </c>
+      <c r="E83" t="s">
         <v>300</v>
-      </c>
-      <c r="C83" t="s">
-        <v>98</v>
-      </c>
-      <c r="D83" t="s">
-        <v>393</v>
-      </c>
-      <c r="E83" t="s">
-        <v>308</v>
       </c>
       <c r="F83" t="b">
         <v>0</v>
@@ -4631,16 +4585,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C84" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D84" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E84" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F84" t="b">
         <v>0</v>
@@ -4652,16 +4606,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D85" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="E85" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F85" t="b">
         <v>0</v>
@@ -4673,16 +4627,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C86" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D86" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="E86" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
@@ -4694,16 +4648,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C87" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D87" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E87" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F87" t="b">
         <v>0</v>
@@ -4715,16 +4669,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>292</v>
+      </c>
+      <c r="C88" t="s">
+        <v>95</v>
+      </c>
+      <c r="D88" t="s">
+        <v>390</v>
+      </c>
+      <c r="E88" t="s">
         <v>300</v>
-      </c>
-      <c r="C88" t="s">
-        <v>103</v>
-      </c>
-      <c r="D88" t="s">
-        <v>398</v>
-      </c>
-      <c r="E88" t="s">
-        <v>308</v>
       </c>
       <c r="F88" t="b">
         <v>0</v>
@@ -4736,16 +4690,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C89" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D89" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="E89" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F89" t="b">
         <v>0</v>
@@ -4757,16 +4711,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C90" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D90" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="E90" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F90" t="b">
         <v>0</v>
@@ -4778,16 +4732,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C91" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D91" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E91" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F91" t="b">
         <v>0</v>
@@ -4799,16 +4753,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C92" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D92" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="E92" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F92" t="b">
         <v>0</v>
@@ -4820,16 +4774,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C93" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D93" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="E93" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F93" t="b">
         <v>0</v>
@@ -4841,16 +4795,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C94" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D94" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="E94" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F94" t="b">
         <v>0</v>
@@ -4862,16 +4816,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C95" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D95" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E95" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F95" t="b">
         <v>0</v>
@@ -4883,16 +4837,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C96" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D96" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="E96" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F96" t="b">
         <v>0</v>
@@ -4904,16 +4858,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>292</v>
+      </c>
+      <c r="C97" t="s">
+        <v>104</v>
+      </c>
+      <c r="D97" t="s">
+        <v>399</v>
+      </c>
+      <c r="E97" t="s">
         <v>300</v>
-      </c>
-      <c r="C97" t="s">
-        <v>112</v>
-      </c>
-      <c r="D97" t="s">
-        <v>407</v>
-      </c>
-      <c r="E97" t="s">
-        <v>308</v>
       </c>
       <c r="F97" t="b">
         <v>0</v>
@@ -4925,16 +4879,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C98" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D98" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="E98" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F98" t="b">
         <v>0</v>
@@ -4946,16 +4900,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C99" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D99" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E99" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F99" t="b">
         <v>0</v>
@@ -4967,16 +4921,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C100" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D100" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E100" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F100" t="b">
         <v>0</v>
@@ -4988,16 +4942,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>292</v>
+      </c>
+      <c r="C101" t="s">
+        <v>108</v>
+      </c>
+      <c r="D101" t="s">
+        <v>403</v>
+      </c>
+      <c r="E101" t="s">
         <v>300</v>
-      </c>
-      <c r="C101" t="s">
-        <v>116</v>
-      </c>
-      <c r="D101" t="s">
-        <v>411</v>
-      </c>
-      <c r="E101" t="s">
-        <v>308</v>
       </c>
       <c r="F101" t="b">
         <v>0</v>
@@ -5009,16 +4963,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C102" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D102" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="E102" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F102" t="b">
         <v>0</v>
@@ -5030,16 +4984,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>292</v>
+      </c>
+      <c r="C103" t="s">
+        <v>110</v>
+      </c>
+      <c r="D103" t="s">
+        <v>405</v>
+      </c>
+      <c r="E103" t="s">
         <v>300</v>
-      </c>
-      <c r="C103" t="s">
-        <v>118</v>
-      </c>
-      <c r="D103" t="s">
-        <v>413</v>
-      </c>
-      <c r="E103" t="s">
-        <v>308</v>
       </c>
       <c r="F103" t="b">
         <v>0</v>
@@ -5051,16 +5005,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C104" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D104" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="E104" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F104" t="b">
         <v>0</v>
@@ -5072,16 +5026,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C105" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D105" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E105" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F105" t="b">
         <v>0</v>
@@ -5093,16 +5047,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C106" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D106" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E106" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F106" t="b">
         <v>0</v>
@@ -5114,16 +5068,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C107" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E107" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F107" t="b">
         <v>0</v>
@@ -5135,16 +5089,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D108" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="E108" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F108" t="b">
         <v>0</v>
@@ -5156,16 +5110,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C109" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D109" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E109" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F109" t="b">
         <v>0</v>
@@ -5177,16 +5131,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C110" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D110" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="E110" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F110" t="b">
         <v>0</v>
@@ -5198,16 +5152,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C111" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D111" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E111" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F111" t="b">
         <v>0</v>
@@ -5219,16 +5173,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C112" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D112" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E112" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F112" t="b">
         <v>0</v>
@@ -5240,16 +5194,16 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C113" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D113" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="E113" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F113" t="b">
         <v>0</v>
@@ -5261,16 +5215,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C114" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D114" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="E114" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F114" t="b">
         <v>0</v>
@@ -5282,16 +5236,16 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C115" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D115" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E115" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F115" t="b">
         <v>0</v>
@@ -5303,16 +5257,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
+        <v>292</v>
+      </c>
+      <c r="C116" t="s">
+        <v>123</v>
+      </c>
+      <c r="D116" t="s">
+        <v>418</v>
+      </c>
+      <c r="E116" t="s">
         <v>300</v>
-      </c>
-      <c r="C116" t="s">
-        <v>131</v>
-      </c>
-      <c r="D116" t="s">
-        <v>426</v>
-      </c>
-      <c r="E116" t="s">
-        <v>308</v>
       </c>
       <c r="F116" t="b">
         <v>0</v>
@@ -5324,16 +5278,16 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
+        <v>292</v>
+      </c>
+      <c r="C117" t="s">
+        <v>124</v>
+      </c>
+      <c r="D117" t="s">
+        <v>419</v>
+      </c>
+      <c r="E117" t="s">
         <v>300</v>
-      </c>
-      <c r="C117" t="s">
-        <v>132</v>
-      </c>
-      <c r="D117" t="s">
-        <v>427</v>
-      </c>
-      <c r="E117" t="s">
-        <v>308</v>
       </c>
       <c r="F117" t="b">
         <v>0</v>
@@ -5345,16 +5299,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C118" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D118" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="E118" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F118" t="b">
         <v>0</v>
@@ -5366,16 +5320,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
+        <v>292</v>
+      </c>
+      <c r="C119" t="s">
+        <v>126</v>
+      </c>
+      <c r="D119" t="s">
+        <v>421</v>
+      </c>
+      <c r="E119" t="s">
         <v>300</v>
-      </c>
-      <c r="C119" t="s">
-        <v>134</v>
-      </c>
-      <c r="D119" t="s">
-        <v>429</v>
-      </c>
-      <c r="E119" t="s">
-        <v>308</v>
       </c>
       <c r="F119" t="b">
         <v>0</v>
@@ -5387,16 +5341,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C120" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D120" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="E120" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F120" t="b">
         <v>0</v>
@@ -5408,16 +5362,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>292</v>
+      </c>
+      <c r="C121" t="s">
+        <v>128</v>
+      </c>
+      <c r="D121" t="s">
+        <v>423</v>
+      </c>
+      <c r="E121" t="s">
         <v>300</v>
-      </c>
-      <c r="C121" t="s">
-        <v>136</v>
-      </c>
-      <c r="D121" t="s">
-        <v>431</v>
-      </c>
-      <c r="E121" t="s">
-        <v>308</v>
       </c>
       <c r="F121" t="b">
         <v>0</v>
@@ -5429,16 +5383,16 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C122" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D122" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E122" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F122" t="b">
         <v>0</v>
@@ -5450,16 +5404,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
+        <v>292</v>
+      </c>
+      <c r="C123" t="s">
+        <v>130</v>
+      </c>
+      <c r="D123" t="s">
+        <v>425</v>
+      </c>
+      <c r="E123" t="s">
         <v>300</v>
-      </c>
-      <c r="C123" t="s">
-        <v>138</v>
-      </c>
-      <c r="D123" t="s">
-        <v>433</v>
-      </c>
-      <c r="E123" t="s">
-        <v>308</v>
       </c>
       <c r="F123" t="b">
         <v>0</v>
@@ -5471,16 +5425,16 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C124" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D124" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="E124" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F124" t="b">
         <v>0</v>
@@ -5492,16 +5446,16 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
+        <v>292</v>
+      </c>
+      <c r="C125" t="s">
+        <v>132</v>
+      </c>
+      <c r="D125" t="s">
+        <v>427</v>
+      </c>
+      <c r="E125" t="s">
         <v>300</v>
-      </c>
-      <c r="C125" t="s">
-        <v>140</v>
-      </c>
-      <c r="D125" t="s">
-        <v>435</v>
-      </c>
-      <c r="E125" t="s">
-        <v>308</v>
       </c>
       <c r="F125" t="b">
         <v>0</v>
@@ -5513,16 +5467,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C126" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D126" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E126" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F126" t="b">
         <v>0</v>
@@ -5534,16 +5488,16 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D127" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F127" t="b">
         <v>0</v>
@@ -5555,16 +5509,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C128" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D128" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F128" t="b">
         <v>0</v>
@@ -5576,16 +5530,16 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
+        <v>293</v>
+      </c>
+      <c r="C129" t="s">
+        <v>136</v>
+      </c>
+      <c r="D129" t="s">
+        <v>431</v>
+      </c>
+      <c r="E129" t="s">
         <v>301</v>
-      </c>
-      <c r="C129" t="s">
-        <v>144</v>
-      </c>
-      <c r="D129" t="s">
-        <v>439</v>
-      </c>
-      <c r="E129" t="s">
-        <v>309</v>
       </c>
       <c r="F129" t="b">
         <v>0</v>
@@ -5597,16 +5551,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C130" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D130" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="E130" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F130" t="b">
         <v>0</v>
@@ -5618,16 +5572,16 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C131" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D131" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E131" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F131" t="b">
         <v>0</v>
@@ -5639,16 +5593,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C132" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D132" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="E132" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F132" t="b">
         <v>0</v>
@@ -5660,16 +5614,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C133" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D133" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="E133" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F133" t="b">
         <v>0</v>
@@ -5681,16 +5635,16 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C134" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D134" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E134" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F134" t="b">
         <v>0</v>
@@ -5702,16 +5656,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
+        <v>293</v>
+      </c>
+      <c r="C135" t="s">
+        <v>142</v>
+      </c>
+      <c r="D135" t="s">
+        <v>437</v>
+      </c>
+      <c r="E135" t="s">
         <v>301</v>
-      </c>
-      <c r="C135" t="s">
-        <v>150</v>
-      </c>
-      <c r="D135" t="s">
-        <v>445</v>
-      </c>
-      <c r="E135" t="s">
-        <v>309</v>
       </c>
       <c r="F135" t="b">
         <v>0</v>
@@ -5723,16 +5677,16 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C136" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D136" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E136" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F136" t="b">
         <v>0</v>
@@ -5744,16 +5698,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
+        <v>293</v>
+      </c>
+      <c r="C137" t="s">
+        <v>144</v>
+      </c>
+      <c r="D137" t="s">
+        <v>439</v>
+      </c>
+      <c r="E137" t="s">
         <v>301</v>
-      </c>
-      <c r="C137" t="s">
-        <v>152</v>
-      </c>
-      <c r="D137" t="s">
-        <v>447</v>
-      </c>
-      <c r="E137" t="s">
-        <v>309</v>
       </c>
       <c r="F137" t="b">
         <v>0</v>
@@ -5765,16 +5719,16 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
+        <v>293</v>
+      </c>
+      <c r="C138" t="s">
+        <v>145</v>
+      </c>
+      <c r="D138" t="s">
+        <v>440</v>
+      </c>
+      <c r="E138" t="s">
         <v>301</v>
-      </c>
-      <c r="C138" t="s">
-        <v>153</v>
-      </c>
-      <c r="D138" t="s">
-        <v>448</v>
-      </c>
-      <c r="E138" t="s">
-        <v>309</v>
       </c>
       <c r="F138" t="b">
         <v>0</v>
@@ -5786,16 +5740,16 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
+        <v>293</v>
+      </c>
+      <c r="C139" t="s">
+        <v>146</v>
+      </c>
+      <c r="D139" t="s">
+        <v>441</v>
+      </c>
+      <c r="E139" t="s">
         <v>301</v>
-      </c>
-      <c r="C139" t="s">
-        <v>154</v>
-      </c>
-      <c r="D139" t="s">
-        <v>449</v>
-      </c>
-      <c r="E139" t="s">
-        <v>309</v>
       </c>
       <c r="F139" t="b">
         <v>0</v>
@@ -5807,16 +5761,16 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
+        <v>293</v>
+      </c>
+      <c r="C140" t="s">
+        <v>147</v>
+      </c>
+      <c r="D140" t="s">
+        <v>442</v>
+      </c>
+      <c r="E140" t="s">
         <v>301</v>
-      </c>
-      <c r="C140" t="s">
-        <v>155</v>
-      </c>
-      <c r="D140" t="s">
-        <v>450</v>
-      </c>
-      <c r="E140" t="s">
-        <v>309</v>
       </c>
       <c r="F140" t="b">
         <v>0</v>
@@ -5828,16 +5782,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C141" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D141" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E141" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F141" t="b">
         <v>0</v>
@@ -5849,16 +5803,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
+        <v>293</v>
+      </c>
+      <c r="C142" t="s">
+        <v>149</v>
+      </c>
+      <c r="D142" t="s">
+        <v>444</v>
+      </c>
+      <c r="E142" t="s">
         <v>301</v>
-      </c>
-      <c r="C142" t="s">
-        <v>157</v>
-      </c>
-      <c r="D142" t="s">
-        <v>452</v>
-      </c>
-      <c r="E142" t="s">
-        <v>309</v>
       </c>
       <c r="F142" t="b">
         <v>0</v>
@@ -5870,16 +5824,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C143" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D143" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="E143" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F143" t="b">
         <v>0</v>
@@ -5891,16 +5845,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C144" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D144" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="E144" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F144" t="b">
         <v>0</v>
@@ -5912,16 +5866,16 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
+        <v>293</v>
+      </c>
+      <c r="C145" t="s">
+        <v>152</v>
+      </c>
+      <c r="D145" t="s">
+        <v>447</v>
+      </c>
+      <c r="E145" t="s">
         <v>301</v>
-      </c>
-      <c r="C145" t="s">
-        <v>160</v>
-      </c>
-      <c r="D145" t="s">
-        <v>455</v>
-      </c>
-      <c r="E145" t="s">
-        <v>309</v>
       </c>
       <c r="F145" t="b">
         <v>0</v>
@@ -5933,16 +5887,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C146" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D146" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="E146" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F146" t="b">
         <v>0</v>
@@ -5954,16 +5908,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
+        <v>293</v>
+      </c>
+      <c r="C147" t="s">
+        <v>154</v>
+      </c>
+      <c r="D147" t="s">
+        <v>449</v>
+      </c>
+      <c r="E147" t="s">
         <v>301</v>
-      </c>
-      <c r="C147" t="s">
-        <v>162</v>
-      </c>
-      <c r="D147" t="s">
-        <v>457</v>
-      </c>
-      <c r="E147" t="s">
-        <v>309</v>
       </c>
       <c r="F147" t="b">
         <v>0</v>
@@ -5975,16 +5929,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D148" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="E148" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F148" t="b">
         <v>0</v>
@@ -5996,16 +5950,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
+        <v>293</v>
+      </c>
+      <c r="C149" t="s">
+        <v>156</v>
+      </c>
+      <c r="D149" t="s">
+        <v>451</v>
+      </c>
+      <c r="E149" t="s">
         <v>301</v>
-      </c>
-      <c r="C149" t="s">
-        <v>164</v>
-      </c>
-      <c r="D149" t="s">
-        <v>459</v>
-      </c>
-      <c r="E149" t="s">
-        <v>309</v>
       </c>
       <c r="F149" t="b">
         <v>0</v>
@@ -6017,16 +5971,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C150" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D150" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="E150" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F150" t="b">
         <v>0</v>
@@ -6038,16 +5992,16 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
+        <v>293</v>
+      </c>
+      <c r="C151" t="s">
+        <v>158</v>
+      </c>
+      <c r="D151" t="s">
+        <v>453</v>
+      </c>
+      <c r="E151" t="s">
         <v>301</v>
-      </c>
-      <c r="C151" t="s">
-        <v>166</v>
-      </c>
-      <c r="D151" t="s">
-        <v>461</v>
-      </c>
-      <c r="E151" t="s">
-        <v>309</v>
       </c>
       <c r="F151" t="b">
         <v>0</v>
@@ -6059,16 +6013,16 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
+        <v>293</v>
+      </c>
+      <c r="C152" t="s">
+        <v>159</v>
+      </c>
+      <c r="D152" t="s">
+        <v>454</v>
+      </c>
+      <c r="E152" t="s">
         <v>301</v>
-      </c>
-      <c r="C152" t="s">
-        <v>167</v>
-      </c>
-      <c r="D152" t="s">
-        <v>462</v>
-      </c>
-      <c r="E152" t="s">
-        <v>309</v>
       </c>
       <c r="F152" t="b">
         <v>0</v>
@@ -6080,16 +6034,16 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C153" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D153" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="E153" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F153" t="b">
         <v>0</v>
@@ -6101,16 +6055,16 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>293</v>
+      </c>
+      <c r="C154" t="s">
+        <v>161</v>
+      </c>
+      <c r="D154" t="s">
+        <v>456</v>
+      </c>
+      <c r="E154" t="s">
         <v>301</v>
-      </c>
-      <c r="C154" t="s">
-        <v>169</v>
-      </c>
-      <c r="D154" t="s">
-        <v>464</v>
-      </c>
-      <c r="E154" t="s">
-        <v>309</v>
       </c>
       <c r="F154" t="b">
         <v>0</v>
@@ -6122,16 +6076,16 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
+        <v>293</v>
+      </c>
+      <c r="C155" t="s">
+        <v>162</v>
+      </c>
+      <c r="D155" t="s">
+        <v>457</v>
+      </c>
+      <c r="E155" t="s">
         <v>301</v>
-      </c>
-      <c r="C155" t="s">
-        <v>170</v>
-      </c>
-      <c r="D155" t="s">
-        <v>465</v>
-      </c>
-      <c r="E155" t="s">
-        <v>309</v>
       </c>
       <c r="F155" t="b">
         <v>0</v>
@@ -6143,16 +6097,16 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C156" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D156" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="E156" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F156" t="b">
         <v>0</v>
@@ -6164,16 +6118,16 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>293</v>
+      </c>
+      <c r="C157" t="s">
+        <v>164</v>
+      </c>
+      <c r="D157" t="s">
+        <v>459</v>
+      </c>
+      <c r="E157" t="s">
         <v>301</v>
-      </c>
-      <c r="C157" t="s">
-        <v>172</v>
-      </c>
-      <c r="D157" t="s">
-        <v>467</v>
-      </c>
-      <c r="E157" t="s">
-        <v>309</v>
       </c>
       <c r="F157" t="b">
         <v>0</v>
@@ -6185,16 +6139,16 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>293</v>
+      </c>
+      <c r="C158" t="s">
+        <v>165</v>
+      </c>
+      <c r="D158" t="s">
+        <v>460</v>
+      </c>
+      <c r="E158" t="s">
         <v>301</v>
-      </c>
-      <c r="C158" t="s">
-        <v>173</v>
-      </c>
-      <c r="D158" t="s">
-        <v>468</v>
-      </c>
-      <c r="E158" t="s">
-        <v>309</v>
       </c>
       <c r="F158" t="b">
         <v>0</v>
@@ -6206,16 +6160,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>293</v>
+      </c>
+      <c r="C159" t="s">
+        <v>166</v>
+      </c>
+      <c r="D159" t="s">
+        <v>461</v>
+      </c>
+      <c r="E159" t="s">
         <v>301</v>
-      </c>
-      <c r="C159" t="s">
-        <v>174</v>
-      </c>
-      <c r="D159" t="s">
-        <v>469</v>
-      </c>
-      <c r="E159" t="s">
-        <v>309</v>
       </c>
       <c r="F159" t="b">
         <v>0</v>
@@ -6227,16 +6181,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C160" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D160" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E160" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F160" t="b">
         <v>0</v>
@@ -6248,16 +6202,16 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
+        <v>293</v>
+      </c>
+      <c r="C161" t="s">
+        <v>168</v>
+      </c>
+      <c r="D161" t="s">
+        <v>463</v>
+      </c>
+      <c r="E161" t="s">
         <v>301</v>
-      </c>
-      <c r="C161" t="s">
-        <v>176</v>
-      </c>
-      <c r="D161" t="s">
-        <v>471</v>
-      </c>
-      <c r="E161" t="s">
-        <v>309</v>
       </c>
       <c r="F161" t="b">
         <v>0</v>
@@ -6269,16 +6223,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C162" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D162" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="E162" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F162" t="b">
         <v>0</v>
@@ -6290,16 +6244,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
+        <v>293</v>
+      </c>
+      <c r="C163" t="s">
+        <v>170</v>
+      </c>
+      <c r="D163" t="s">
+        <v>465</v>
+      </c>
+      <c r="E163" t="s">
         <v>301</v>
-      </c>
-      <c r="C163" t="s">
-        <v>178</v>
-      </c>
-      <c r="D163" t="s">
-        <v>473</v>
-      </c>
-      <c r="E163" t="s">
-        <v>309</v>
       </c>
       <c r="F163" t="b">
         <v>0</v>
@@ -6311,16 +6265,16 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C164" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D164" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="E164" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F164" t="b">
         <v>0</v>
@@ -6332,16 +6286,16 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
+        <v>293</v>
+      </c>
+      <c r="C165" t="s">
+        <v>172</v>
+      </c>
+      <c r="D165" t="s">
+        <v>467</v>
+      </c>
+      <c r="E165" t="s">
         <v>301</v>
-      </c>
-      <c r="C165" t="s">
-        <v>180</v>
-      </c>
-      <c r="D165" t="s">
-        <v>475</v>
-      </c>
-      <c r="E165" t="s">
-        <v>309</v>
       </c>
       <c r="F165" t="b">
         <v>0</v>
@@ -6353,16 +6307,16 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C166" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D166" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="E166" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F166" t="b">
         <v>0</v>
@@ -6374,16 +6328,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C167" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D167" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="E167" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F167" t="b">
         <v>0</v>
@@ -6395,16 +6349,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
+        <v>293</v>
+      </c>
+      <c r="C168" t="s">
+        <v>175</v>
+      </c>
+      <c r="D168" t="s">
+        <v>470</v>
+      </c>
+      <c r="E168" t="s">
         <v>301</v>
-      </c>
-      <c r="C168" t="s">
-        <v>183</v>
-      </c>
-      <c r="D168" t="s">
-        <v>478</v>
-      </c>
-      <c r="E168" t="s">
-        <v>309</v>
       </c>
       <c r="F168" t="b">
         <v>0</v>
@@ -6416,16 +6370,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
+        <v>293</v>
+      </c>
+      <c r="C169" t="s">
+        <v>176</v>
+      </c>
+      <c r="D169" t="s">
+        <v>471</v>
+      </c>
+      <c r="E169" t="s">
         <v>301</v>
-      </c>
-      <c r="C169" t="s">
-        <v>184</v>
-      </c>
-      <c r="D169" t="s">
-        <v>479</v>
-      </c>
-      <c r="E169" t="s">
-        <v>309</v>
       </c>
       <c r="F169" t="b">
         <v>0</v>
@@ -6437,16 +6391,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
+        <v>293</v>
+      </c>
+      <c r="C170" t="s">
+        <v>177</v>
+      </c>
+      <c r="D170" t="s">
+        <v>472</v>
+      </c>
+      <c r="E170" t="s">
         <v>301</v>
-      </c>
-      <c r="C170" t="s">
-        <v>185</v>
-      </c>
-      <c r="D170" t="s">
-        <v>480</v>
-      </c>
-      <c r="E170" t="s">
-        <v>309</v>
       </c>
       <c r="F170" t="b">
         <v>0</v>
@@ -6458,16 +6412,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C171" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D171" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="E171" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F171" t="b">
         <v>0</v>
@@ -6479,16 +6433,16 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C172" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D172" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E172" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F172" t="b">
         <v>0</v>
@@ -6500,16 +6454,16 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C173" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D173" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="E173" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F173" t="b">
         <v>0</v>
@@ -6521,16 +6475,16 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C174" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D174" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="E174" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F174" t="b">
         <v>0</v>
@@ -6542,16 +6496,16 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C175" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D175" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="E175" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F175" t="b">
         <v>0</v>
@@ -6563,16 +6517,16 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C176" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D176" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="E176" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F176" t="b">
         <v>0</v>
@@ -6584,16 +6538,16 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C177" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D177" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="E177" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F177" t="b">
         <v>0</v>
@@ -6605,16 +6559,16 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
+        <v>293</v>
+      </c>
+      <c r="C178" t="s">
+        <v>185</v>
+      </c>
+      <c r="D178" t="s">
+        <v>480</v>
+      </c>
+      <c r="E178" t="s">
         <v>301</v>
-      </c>
-      <c r="C178" t="s">
-        <v>193</v>
-      </c>
-      <c r="D178" t="s">
-        <v>488</v>
-      </c>
-      <c r="E178" t="s">
-        <v>309</v>
       </c>
       <c r="F178" t="b">
         <v>0</v>
@@ -6626,16 +6580,16 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C179" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D179" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E179" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F179" t="b">
         <v>0</v>
@@ -6647,16 +6601,16 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
+        <v>293</v>
+      </c>
+      <c r="C180" t="s">
+        <v>187</v>
+      </c>
+      <c r="D180" t="s">
+        <v>482</v>
+      </c>
+      <c r="E180" t="s">
         <v>301</v>
-      </c>
-      <c r="C180" t="s">
-        <v>195</v>
-      </c>
-      <c r="D180" t="s">
-        <v>490</v>
-      </c>
-      <c r="E180" t="s">
-        <v>309</v>
       </c>
       <c r="F180" t="b">
         <v>0</v>
@@ -6668,16 +6622,16 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C181" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D181" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="E181" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F181" t="b">
         <v>0</v>
@@ -6689,16 +6643,16 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
+        <v>293</v>
+      </c>
+      <c r="C182" t="s">
+        <v>189</v>
+      </c>
+      <c r="D182" t="s">
+        <v>484</v>
+      </c>
+      <c r="E182" t="s">
         <v>301</v>
-      </c>
-      <c r="C182" t="s">
-        <v>197</v>
-      </c>
-      <c r="D182" t="s">
-        <v>492</v>
-      </c>
-      <c r="E182" t="s">
-        <v>309</v>
       </c>
       <c r="F182" t="b">
         <v>0</v>
@@ -6710,16 +6664,16 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C183" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D183" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="E183" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F183" t="b">
         <v>0</v>
@@ -6731,16 +6685,16 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C184" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D184" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="E184" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F184" t="b">
         <v>0</v>
@@ -6752,16 +6706,16 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C185" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D185" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="E185" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F185" t="b">
         <v>0</v>
@@ -6773,16 +6727,16 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C186" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D186" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="E186" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F186" t="b">
         <v>0</v>
@@ -6794,16 +6748,16 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C187" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D187" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="E187" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F187" t="b">
         <v>0</v>
@@ -6815,16 +6769,16 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
+        <v>293</v>
+      </c>
+      <c r="C188" t="s">
+        <v>195</v>
+      </c>
+      <c r="D188" t="s">
+        <v>490</v>
+      </c>
+      <c r="E188" t="s">
         <v>301</v>
-      </c>
-      <c r="C188" t="s">
-        <v>203</v>
-      </c>
-      <c r="D188" t="s">
-        <v>498</v>
-      </c>
-      <c r="E188" t="s">
-        <v>309</v>
       </c>
       <c r="F188" t="b">
         <v>0</v>
@@ -6836,16 +6790,16 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C189" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D189" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="E189" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F189" t="b">
         <v>0</v>
@@ -6857,16 +6811,16 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C190" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D190" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="E190" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F190" t="b">
         <v>0</v>
@@ -6878,16 +6832,16 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C191" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D191" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="E191" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F191" t="b">
         <v>0</v>
@@ -6899,16 +6853,16 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C192" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D192" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="E192" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F192" t="b">
         <v>0</v>
@@ -6920,16 +6874,16 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C193" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D193" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="E193" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F193" t="b">
         <v>0</v>
@@ -6941,16 +6895,16 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C194" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D194" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="E194" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F194" t="b">
         <v>0</v>
@@ -6962,16 +6916,16 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C195" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D195" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="E195" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F195" t="b">
         <v>0</v>
@@ -6983,16 +6937,16 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C196" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D196" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E196" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F196" t="b">
         <v>0</v>
@@ -7004,16 +6958,16 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C197" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D197" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="E197" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F197" t="b">
         <v>0</v>
@@ -7025,16 +6979,16 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C198" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D198" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="E198" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F198" t="b">
         <v>0</v>
@@ -7046,16 +7000,16 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C199" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D199" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E199" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F199" t="b">
         <v>0</v>
@@ -7067,16 +7021,16 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C200" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D200" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E200" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F200" t="b">
         <v>0</v>
@@ -7088,16 +7042,16 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C201" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D201" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="E201" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F201" t="b">
         <v>0</v>
@@ -7109,16 +7063,16 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C202" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D202" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="E202" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F202" t="b">
         <v>0</v>
@@ -7130,16 +7084,16 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C203" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D203" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="E203" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F203" t="b">
         <v>0</v>
@@ -7151,16 +7105,16 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C204" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D204" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="E204" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F204" t="b">
         <v>0</v>
@@ -7172,16 +7126,16 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C205" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D205" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="E205" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F205" t="b">
         <v>0</v>
@@ -7193,16 +7147,16 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C206" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D206" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="E206" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F206" t="b">
         <v>0</v>
@@ -7214,16 +7168,16 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C207" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D207" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="E207" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F207" t="b">
         <v>0</v>
@@ -7235,16 +7189,16 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C208" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D208" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="E208" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F208" t="b">
         <v>0</v>
@@ -7256,16 +7210,16 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C209" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D209" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="E209" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F209" t="b">
         <v>0</v>
@@ -7277,16 +7231,16 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C210" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D210" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="E210" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F210" t="b">
         <v>0</v>
@@ -7298,16 +7252,16 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C211" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D211" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="E211" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F211" t="b">
         <v>0</v>
@@ -7319,16 +7273,16 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C212" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D212" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="E212" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F212" t="b">
         <v>0</v>
@@ -7340,16 +7294,16 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C213" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D213" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="E213" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F213" t="b">
         <v>0</v>
@@ -7361,16 +7315,16 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C214" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D214" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="E214" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F214" t="b">
         <v>0</v>
@@ -7382,16 +7336,16 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C215" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D215" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="E215" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F215" t="b">
         <v>0</v>
@@ -7403,16 +7357,16 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C216" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D216" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="E216" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F216" t="b">
         <v>0</v>
@@ -7424,16 +7378,16 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C217" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D217" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="E217" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F217" t="b">
         <v>0</v>
@@ -7445,16 +7399,16 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C218" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D218" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="E218" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F218" t="b">
         <v>0</v>
@@ -7466,16 +7420,16 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C219" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D219" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="E219" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F219" t="b">
         <v>0</v>
@@ -7487,16 +7441,16 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C220" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D220" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="E220" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F220" t="b">
         <v>0</v>
@@ -7508,16 +7462,16 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C221" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D221" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="E221" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F221" t="b">
         <v>0</v>
@@ -7529,16 +7483,16 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
+        <v>295</v>
+      </c>
+      <c r="C222" t="s">
         <v>303</v>
       </c>
-      <c r="C222" t="s">
-        <v>311</v>
-      </c>
       <c r="D222" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E222" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F222" t="b">
         <v>1</v>
@@ -7550,16 +7504,16 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C223" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D223" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="E223" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F223" t="b">
         <v>0</v>
@@ -7571,16 +7525,16 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C224" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D224" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="E224" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F224" t="b">
         <v>0</v>
@@ -7592,16 +7546,16 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C225" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D225" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E225" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F225" t="b">
         <v>0</v>
@@ -7613,16 +7567,16 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C226" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D226" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="E226" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F226" t="b">
         <v>0</v>
@@ -7634,16 +7588,16 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C227" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D227" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="E227" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F227" t="b">
         <v>0</v>
@@ -7655,16 +7609,16 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C228" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="D228" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="E228" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F228" t="b">
         <v>0</v>
@@ -7676,16 +7630,16 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C229" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D229" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="E229" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F229" t="b">
         <v>0</v>
@@ -7697,16 +7651,16 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C230" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D230" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E230" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F230" t="b">
         <v>0</v>
@@ -7718,16 +7672,16 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C231" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D231" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="E231" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F231" t="b">
         <v>0</v>
@@ -7739,16 +7693,16 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C232" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D232" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="E232" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F232" t="b">
         <v>0</v>
@@ -7760,16 +7714,16 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C233" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D233" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="E233" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F233" t="b">
         <v>0</v>
@@ -7781,16 +7735,16 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C234" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D234" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="E234" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F234" t="b">
         <v>0</v>
@@ -7802,16 +7756,16 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C235" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D235" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E235" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F235" t="b">
         <v>0</v>
@@ -7823,16 +7777,16 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C236" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D236" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="E236" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F236" t="b">
         <v>0</v>
@@ -7844,16 +7798,16 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C237" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D237" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="E237" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F237" t="b">
         <v>0</v>
@@ -7865,16 +7819,16 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C238" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D238" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="E238" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F238" t="b">
         <v>0</v>
@@ -7886,16 +7840,16 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C239" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D239" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="E239" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F239" t="b">
         <v>0</v>
@@ -7907,16 +7861,16 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C240" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D240" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E240" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F240" t="b">
         <v>0</v>
@@ -7928,16 +7882,16 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C241" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D241" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="E241" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F241" t="b">
         <v>0</v>
@@ -7949,16 +7903,16 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C242" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="D242" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="E242" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F242" t="b">
         <v>0</v>
@@ -7970,16 +7924,16 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C243" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="D243" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="E243" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F243" t="b">
         <v>0</v>
@@ -7991,16 +7945,16 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C244" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D244" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="E244" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F244" t="b">
         <v>0</v>
@@ -8012,16 +7966,16 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C245" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D245" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="E245" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F245" t="b">
         <v>0</v>
@@ -8033,16 +7987,16 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D246" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="E246" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F246" t="b">
         <v>0</v>
@@ -8054,16 +8008,16 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C247" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D247" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="E247" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F247" t="b">
         <v>0</v>
@@ -8075,16 +8029,16 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D248" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="E248" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F248" t="b">
         <v>0</v>
@@ -8096,16 +8050,16 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C249" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D249" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="E249" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F249" t="b">
         <v>0</v>
@@ -8117,16 +8071,16 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C250" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D250" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="E250" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F250" t="b">
         <v>0</v>
@@ -8138,16 +8092,16 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C251" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D251" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="E251" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F251" t="b">
         <v>0</v>
@@ -8159,16 +8113,16 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C252" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D252" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="E252" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F252" t="b">
         <v>0</v>
@@ -8180,16 +8134,16 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C253" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="D253" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="E253" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F253" t="b">
         <v>0</v>
@@ -8201,16 +8155,16 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C254" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D254" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="E254" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F254" t="b">
         <v>0</v>
@@ -8222,16 +8176,16 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C255" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="E255" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F255" t="b">
         <v>0</v>
@@ -8243,16 +8197,16 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C256" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D256" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="E256" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F256" t="b">
         <v>0</v>
@@ -8264,16 +8218,16 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C257" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D257" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="E257" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F257" t="b">
         <v>0</v>
@@ -8285,16 +8239,16 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C258" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D258" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="E258" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F258" t="b">
         <v>0</v>
@@ -8306,16 +8260,16 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C259" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D259" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="E259" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F259" t="b">
         <v>0</v>
@@ -8327,16 +8281,16 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C260" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D260" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="E260" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F260" t="b">
         <v>0</v>
@@ -8348,16 +8302,16 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C261" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="D261" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E261" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F261" t="b">
         <v>0</v>
@@ -8369,16 +8323,16 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C262" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D262" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="E262" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F262" t="b">
         <v>0</v>
@@ -8390,16 +8344,16 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C263" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D263" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="E263" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F263" t="b">
         <v>0</v>
@@ -8411,16 +8365,16 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C264" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D264" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="E264" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F264" t="b">
         <v>0</v>
@@ -8432,16 +8386,16 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C265" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D265" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="E265" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F265" t="b">
         <v>0</v>
@@ -8453,16 +8407,16 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C266" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D266" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="E266" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F266" t="b">
         <v>0</v>
@@ -8474,16 +8428,16 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C267" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="D267" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="E267" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F267" t="b">
         <v>0</v>
@@ -8495,16 +8449,16 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C268" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D268" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="E268" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F268" t="b">
         <v>0</v>
@@ -8516,16 +8470,16 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C269" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D269" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="E269" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F269" t="b">
         <v>0</v>
@@ -8537,16 +8491,16 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C270" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D270" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="E270" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="F270" t="b">
         <v>0</v>
@@ -8558,16 +8512,16 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C271" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="D271" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="E271" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F271" t="b">
         <v>0</v>
@@ -8579,16 +8533,16 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C272" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D272" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="E272" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F272" t="b">
         <v>0</v>
@@ -8600,16 +8554,16 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C273" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D273" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="E273" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F273" t="b">
         <v>0</v>
@@ -8621,16 +8575,16 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C274" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D274" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="E274" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F274" t="b">
         <v>0</v>
@@ -8642,16 +8596,16 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D275" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="E275" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F275" t="b">
         <v>0</v>
@@ -8663,16 +8617,16 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C276" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D276" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="E276" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F276" t="b">
         <v>0</v>
@@ -8684,16 +8638,16 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C277" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D277" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="E277" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F277" t="b">
         <v>0</v>
@@ -8705,16 +8659,16 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C278" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="D278" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="E278" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F278" t="b">
         <v>0</v>
@@ -8726,16 +8680,16 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C279" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D279" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="E279" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F279" t="b">
         <v>0</v>
@@ -8747,16 +8701,16 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C280" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D280" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="E280" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F280" t="b">
         <v>0</v>
@@ -8768,16 +8722,16 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C281" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D281" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="E281" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F281" t="b">
         <v>0</v>
@@ -8792,7 +8746,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CC9836-71F6-4801-9ED5-83CF14DFE1E5}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -8815,242 +8769,17 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2">
-        <f t="shared" ref="A2:A17" si="0">ROW()-1</f>
+        <f t="shared" ref="A2" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="C2" s="2">
-        <v>46115</v>
+        <v>46262</v>
       </c>
       <c r="D2" s="2">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>593</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46118</v>
-      </c>
-      <c r="D3" s="2">
-        <v>46121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>594</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46122</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46125</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46127</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46128</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46128</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46132</v>
-      </c>
-      <c r="D8" s="2">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46139</v>
-      </c>
-      <c r="D9" s="2">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46142</v>
-      </c>
-      <c r="D10" s="2">
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46143</v>
-      </c>
-      <c r="D11" s="2">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2">
-        <v>46149</v>
-      </c>
-      <c r="D12" s="2">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="2">
-        <v>46153</v>
-      </c>
-      <c r="D13" s="2">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="2">
-        <v>46160</v>
-      </c>
-      <c r="D14" s="2">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2">
-        <v>46161</v>
-      </c>
-      <c r="D15" s="2">
-        <v>46161</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="2">
-        <v>46162</v>
-      </c>
-      <c r="D16" s="2">
-        <v>46163</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="2">
-        <v>46167</v>
-      </c>
-      <c r="D17" s="2">
-        <v>46171</v>
+        <v>46278</v>
       </c>
     </row>
   </sheetData>
